--- a/docs/experiment_metrics.xlsx
+++ b/docs/experiment_metrics.xlsx
@@ -1174,67 +1174,33 @@
           <t>LEVIR-CD-256</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr"/>
-      <c r="G1" t="inlineStr"/>
-      <c r="H1" t="inlineStr"/>
-      <c r="I1" t="inlineStr"/>
-      <c r="J1" t="inlineStr"/>
       <c r="K1" t="inlineStr">
         <is>
           <t>SYSU-CD-256</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr"/>
-      <c r="M1" t="inlineStr"/>
-      <c r="N1" t="inlineStr"/>
-      <c r="O1" t="inlineStr"/>
-      <c r="P1" t="inlineStr"/>
       <c r="Q1" t="inlineStr">
         <is>
           <t>WHU-CD-256</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr"/>
-      <c r="S1" t="inlineStr"/>
-      <c r="T1" t="inlineStr"/>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>CDD-CD-256</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr"/>
-      <c r="Y1" t="inlineStr"/>
-      <c r="Z1" t="inlineStr"/>
-      <c r="AA1" t="inlineStr"/>
-      <c r="AB1" t="inlineStr"/>
       <c r="AC1" t="inlineStr">
         <is>
           <t>LEVIR-CD+256</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr"/>
-      <c r="AE1" t="inlineStr"/>
-      <c r="AF1" t="inlineStr"/>
-      <c r="AG1" t="inlineStr"/>
-      <c r="AH1" t="inlineStr"/>
       <c r="AI1" t="inlineStr">
         <is>
           <t>DSIFN</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr"/>
-      <c r="AK1" t="inlineStr"/>
-      <c r="AL1" t="inlineStr"/>
-      <c r="AM1" t="inlineStr"/>
-      <c r="AN1" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>Recall</t>
@@ -1523,7 +1489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y9"/>
+  <dimension ref="A1:Y11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2256,6 +2222,140 @@
         <v>93.39</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A2Net_LWGANet_L0</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>GRAFT-PLUG Run1 R0</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>saved_models/GRAFT-PLUG/Run1/R0/SYSU-CD-256/train_log.txt</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>LWGANet-L0</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="O10" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>256</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.9222</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.8304</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.8072</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.855</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A2Net_LWGANet_L0</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>GRAFT-PLUG Run1 R0</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CDD-CD-256</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>saved_models/GRAFT-PLUG/Run1/R0/CDD-CD-256/train_log.txt</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>LWGANet-L0</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="O11" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>256</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.9931</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.9476</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.9731</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.9681</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.9781</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.9691</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/experiment_metrics.xlsx
+++ b/docs/experiment_metrics.xlsx
@@ -1489,7 +1489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y11"/>
+  <dimension ref="A1:Y17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2356,6 +2356,408 @@
         <v>0.9691</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>A2Net_LWGANet_L0</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>GRAFT-PLUG Run1 R1-T</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>saved_models/GRAFT-PLUG/Run1/R1-T/SYSU-CD-256/train_log.txt</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>LWGANet-L0</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="O12" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>256</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.9223</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.7087</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.8295</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.8013</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.8598</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.7793</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>A2Net_LWGANet_L0</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>GRAFT-PLUG Run1 R1-T</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>CDD-CD-256</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>saved_models/GRAFT-PLUG/Run1/R1-T/CDD-CD-256/train_log.txt</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>LWGANet-L0</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="O13" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>256</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.9931</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.9474</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.973</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.9688</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.9772</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.969</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>A2Net_LWGANet_L0</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>GRAFT-PLUG Run1 R1-D</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>saved_models/GRAFT-PLUG/Run1/R1-D/SYSU-CD-256/train_log.txt</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>LWGANet-L0</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="O14" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>256</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.9229000000000001</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.7113</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.8313</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.806</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.8583</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.7813</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>A2Net_LWGANet_L0</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>GRAFT-PLUG Run1 R1-U</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>saved_models/GRAFT-PLUG/Run1/R1-U/SYSU-CD-256/train_log.txt</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>LWGANet-L0</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="O15" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>256</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.9208</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.7136</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.8328</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.8362000000000001</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.8294</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.781</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>A2Net_LWGANet_L0</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>GRAFT-PLUG Run1 R1-F</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>saved_models/GRAFT-PLUG/Run1/R1-F/SYSU-CD-256/train_log.txt</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>LWGANet-L0</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="O16" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>256</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.9232</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.7096</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.8300999999999999</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.7961</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.8672</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.7806</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>A2Net_LWGANet_L0</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>GRAFT-PLUG Run1 R1-L</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>SYSU-CD-256</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>saved_models/GRAFT-PLUG/Run1/R1-L/SYSU-CD-256/train_log.txt</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>LWGANet-L0</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>6.74</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.0005</v>
+      </c>
+      <c r="O17" t="n">
+        <v>64</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>256</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.9222</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.7086</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.8295</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.8025</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.8583</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.7791</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
